--- a/Excel/账号密码.xlsx
+++ b/Excel/账号密码.xlsx
@@ -4,12 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9105"/>
+    <workbookView windowWidth="21600" windowHeight="9105" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +28,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+  <si>
+    <t>序号</t>
+  </si>
   <si>
     <t>账号</t>
   </si>
@@ -665,7 +667,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -673,6 +675,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -986,54 +994,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="2" width="17.4690265486726" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="3" width="17.4690265486726" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
         <v>7398479374</v>
       </c>
-      <c r="B2" s="2">
+      <c r="C2" s="3">
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2">
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
         <v>60003152</v>
       </c>
-      <c r="B3" s="2">
+      <c r="C3" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2">
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
         <v>60003152</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="C4" s="3"/>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2">
-        <v>60003152</v>
-      </c>
-      <c r="B5" s="2">
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>60003152.1</v>
+      </c>
+      <c r="C5" s="3">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2">
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3">
         <v>3213131</v>
       </c>
     </row>
@@ -1047,58 +1074,77 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="2" width="18.2654867256637" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="3" width="18.2654867256637" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="2">
+    <row r="2" spans="1:3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
         <v>60003152</v>
       </c>
-      <c r="B2" s="2">
+      <c r="C2" s="2">
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2">
+    <row r="3" spans="1:3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
         <v>60003154</v>
       </c>
-      <c r="B3" s="2">
+      <c r="C3" s="2">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="2">
+    <row r="4" spans="1:3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
         <v>60003159</v>
       </c>
-      <c r="B4" s="2">
+      <c r="C4" s="2">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2">
+    <row r="5" spans="1:3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
         <v>60003152</v>
       </c>
-      <c r="B5" s="2">
+      <c r="C5" s="2">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="2">
+    <row r="6" spans="1:3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
         <v>60003152</v>
       </c>
-      <c r="B6" s="2">
+      <c r="C6" s="2">
         <v>123</v>
       </c>
     </row>
@@ -1107,16 +1153,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/Excel/账号密码.xlsx
+++ b/Excel/账号密码.xlsx
@@ -1142,7 +1142,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>60003152</v>
+        <v>60003156</v>
       </c>
       <c r="C6" s="2">
         <v>123</v>
